--- a/scalability evaluation/input samples/sample_10.xlsx
+++ b/scalability evaluation/input samples/sample_10.xlsx
@@ -442,101 +442,101 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6084</v>
+        <v>1624</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Q55902846</t>
+          <t>Q115043621</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>5023</v>
+        <v>6760</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Q33198462</t>
+          <t>Q21573510</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>5236</v>
+        <v>5421</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Q3909446</t>
+          <t>Q16358809</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7082</v>
+        <v>4344</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Q77877606</t>
+          <t>Q138031795</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3521</v>
+        <v>2673</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Q16191970</t>
+          <t>Q123876853</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>921</v>
+        <v>11365</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q111064496</t>
+          <t>Q65566564</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1315</v>
+        <v>11631</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Q111139816</t>
+          <t>Q65587517</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>7205</v>
+        <v>3473</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Q8063273</t>
+          <t>Q130620130</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4328</v>
+        <v>8887</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Q25443487</t>
+          <t>Q4316586</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>6428</v>
+        <v>6520</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Q6275139</t>
+          <t>Q20512914</t>
         </is>
       </c>
     </row>
